--- a/evaluation/results/Quantitative Evaluation.xlsx
+++ b/evaluation/results/Quantitative Evaluation.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SadruddinS\Data\GermEval25\Quantitative Evaluations\With LA2I2F\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSouzaJ\Datasets\subject-indexing-dataset\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A61AB5-722B-4022-A403-4A40B8EF3826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10200" windowHeight="1800"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall Leaderboard" sheetId="1" r:id="rId1"/>
@@ -22,12 +23,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="48">
   <si>
     <t>Rank</t>
   </si>
@@ -66,12 +70,6 @@
   </si>
   <si>
     <t>en</t>
-  </si>
-  <si>
-    <t>Annif</t>
-  </si>
-  <si>
-    <t>DNB-AI-Project</t>
   </si>
   <si>
     <t>ndcg@5</t>
@@ -161,17 +159,32 @@
     <t>K@20</t>
   </si>
   <si>
-    <t>LA²I²F</t>
+    <t>System 1</t>
+  </si>
+  <si>
+    <t>System 2</t>
+  </si>
+  <si>
+    <t>System 3</t>
+  </si>
+  <si>
+    <t>nDCG@5</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>English</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,6 +196,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -241,10 +262,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -274,10 +296,29 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -289,11 +330,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -307,6 +349,2300 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Record Type Leaderboard'!$X$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>System 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Record Type Leaderboard'!$W$16:$W$20</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Article</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Book</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Conference</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Report</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Thesis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Record Type Leaderboard'!$X$16:$X$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.519502733480118</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.38496465732607199</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.36254670075916001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.389080504930851</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.23199580861774199</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AAC3-4EB1-911C-CBE878D31D61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Record Type Leaderboard'!$Y$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>System 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Record Type Leaderboard'!$W$16:$W$20</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Article</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Book</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Conference</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Report</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Thesis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Record Type Leaderboard'!$Y$16:$Y$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.385488264884293</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.50638092228877496</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.48804357159362599</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.47818063909208902</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.43327115108686198</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AAC3-4EB1-911C-CBE878D31D61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Record Type Leaderboard'!$Z$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>System 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.6666666666666691E-2"/>
+                  <c:y val="-4.2437781360066642E-17"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-AAC3-4EB1-911C-CBE878D31D61}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Record Type Leaderboard'!$W$16:$W$20</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Article</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Book</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Conference</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Report</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Thesis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Record Type Leaderboard'!$Z$16:$Z$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.38503348238878199</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.61973888754940198</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.60433751348826104</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60418008525687406</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.53310659993139498</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-AAC3-4EB1-911C-CBE878D31D61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="450349328"/>
+        <c:axId val="450348848"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="450349328"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450348848"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="450348848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450349328"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.37988430446194232"/>
+          <c:y val="3.3898299052751622E-2"/>
+          <c:w val="0.43520177077932626"/>
+          <c:h val="6.541288638132832E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup orientation="portrait"/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Language Leaderboard'!$U$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>German</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Language Leaderboard'!$V$6:$X$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>System 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>System 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>System 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Language Leaderboard'!$V$7:$X$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.35580137223333003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.521014872790316</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.62367526026213604</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-414D-4908-9068-95C763F29E5F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Language Leaderboard'!$U$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>English</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Language Leaderboard'!$V$6:$X$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>System 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>System 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>System 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Language Leaderboard'!$V$8:$X$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.37792989198736099</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.44109788431775299</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.56429030658716905</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-414D-4908-9068-95C763F29E5F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="136639024"/>
+        <c:axId val="136639504"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="136639024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="136639504"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="136639504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="136639024"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.2234071577173255"/>
+          <c:y val="3.7825049713631612E-2"/>
+          <c:w val="0.40156883399608495"/>
+          <c:h val="0.10638369690718169"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266702</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36A86207-1C96-DC83-E06A-05A2BA008357}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56703734-3DBB-D561-3A9D-46F6155CFBCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -571,16 +2907,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.5703125" bestFit="1" customWidth="1"/>
@@ -615,64 +2951,64 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -680,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1">
         <v>8</v>
@@ -754,7 +3090,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1">
         <v>5</v>
@@ -895,6 +3231,74 @@
       </c>
       <c r="X4" s="7">
         <v>0.116288485937023</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C10" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.36386617248151898</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.39768849252111499</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.41431058453764302</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0.42465193951577102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.491888905232162</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.488026529520386</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.48794211941719801</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0.48793928854573099</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0.60203224959272506</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.63906639008788102</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0.65604758529723195</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0.66516123606597299</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +3308,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -924,89 +3328,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="I2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="M2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="N2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
+      <c r="A3" s="21"/>
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -1060,7 +3464,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
+      <c r="A4" s="21"/>
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1114,7 +3518,7 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
+      <c r="A5" s="21"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1168,7 +3572,7 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="A6" s="21"/>
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -1222,7 +3626,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+      <c r="A7" s="21"/>
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1276,7 +3680,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
+      <c r="A8" s="21"/>
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -1330,7 +3734,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
+      <c r="A9" s="21"/>
       <c r="B9" t="s">
         <v>9</v>
       </c>
@@ -1384,7 +3788,7 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
+      <c r="A10" s="21"/>
       <c r="B10" t="s">
         <v>9</v>
       </c>
@@ -1438,7 +3842,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
+      <c r="A11" s="21"/>
       <c r="B11" t="s">
         <v>10</v>
       </c>
@@ -1492,7 +3896,7 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+      <c r="A12" s="21"/>
       <c r="B12" t="s">
         <v>10</v>
       </c>
@@ -1546,89 +3950,89 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="16" t="s">
+      <c r="A15" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="20" t="s">
+      <c r="D15" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="24"/>
       <c r="D16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="H16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="I16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="L16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="M16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="N16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="6" t="s">
+      <c r="Q16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="R16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="Q16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
+      <c r="A17" s="21"/>
       <c r="B17" t="s">
         <v>6</v>
       </c>
@@ -1682,7 +4086,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
+      <c r="A18" s="21"/>
       <c r="B18" t="s">
         <v>6</v>
       </c>
@@ -1736,7 +4140,7 @@
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
+      <c r="A19" s="21"/>
       <c r="B19" t="s">
         <v>7</v>
       </c>
@@ -1790,7 +4194,7 @@
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
+      <c r="A20" s="21"/>
       <c r="B20" t="s">
         <v>7</v>
       </c>
@@ -1844,7 +4248,7 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
+      <c r="A21" s="21"/>
       <c r="B21" t="s">
         <v>8</v>
       </c>
@@ -1898,7 +4302,7 @@
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
+      <c r="A22" s="21"/>
       <c r="B22" t="s">
         <v>8</v>
       </c>
@@ -1952,7 +4356,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
+      <c r="A23" s="21"/>
       <c r="B23" t="s">
         <v>9</v>
       </c>
@@ -2006,7 +4410,7 @@
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
+      <c r="A24" s="21"/>
       <c r="B24" t="s">
         <v>9</v>
       </c>
@@ -2060,7 +4464,7 @@
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
+      <c r="A25" s="21"/>
       <c r="B25" t="s">
         <v>10</v>
       </c>
@@ -2114,7 +4518,7 @@
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
+      <c r="A26" s="21"/>
       <c r="B26" t="s">
         <v>10</v>
       </c>
@@ -2168,89 +4572,89 @@
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="15"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="24"/>
       <c r="D30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="H30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="I30" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="L30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="M30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="N30" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O30" s="6" t="s">
+      <c r="Q30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="P30" s="6" t="s">
+      <c r="R30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="Q30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R30" s="6" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
+      <c r="A31" s="21"/>
       <c r="B31" t="s">
         <v>6</v>
       </c>
@@ -2304,7 +4708,7 @@
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
+      <c r="A32" s="21"/>
       <c r="B32" t="s">
         <v>6</v>
       </c>
@@ -2358,7 +4762,7 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
+      <c r="A33" s="21"/>
       <c r="B33" t="s">
         <v>7</v>
       </c>
@@ -2412,7 +4816,7 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
+      <c r="A34" s="21"/>
       <c r="B34" t="s">
         <v>7</v>
       </c>
@@ -2466,7 +4870,7 @@
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
+      <c r="A35" s="21"/>
       <c r="B35" t="s">
         <v>8</v>
       </c>
@@ -2520,7 +4924,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
+      <c r="A36" s="21"/>
       <c r="B36" t="s">
         <v>8</v>
       </c>
@@ -2574,7 +4978,7 @@
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
+      <c r="A37" s="21"/>
       <c r="B37" t="s">
         <v>9</v>
       </c>
@@ -2628,7 +5032,7 @@
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
+      <c r="A38" s="21"/>
       <c r="B38" t="s">
         <v>9</v>
       </c>
@@ -2682,7 +5086,7 @@
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
+      <c r="A39" s="21"/>
       <c r="B39" t="s">
         <v>10</v>
       </c>
@@ -2736,7 +5140,7 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
+      <c r="A40" s="21"/>
       <c r="B40" t="s">
         <v>10</v>
       </c>
@@ -2790,89 +5194,89 @@
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="O43" s="15"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="15"/>
-      <c r="R43" s="15"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="O43" s="23"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="23"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="17"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="24"/>
       <c r="D44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="H44" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="I44" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="L44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K44" s="5" t="s">
+      <c r="M44" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="N44" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O44" s="6" t="s">
+      <c r="Q44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="P44" s="6" t="s">
+      <c r="R44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="Q44" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R44" s="6" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
+      <c r="A45" s="21"/>
       <c r="B45" t="s">
         <v>6</v>
       </c>
@@ -2926,7 +5330,7 @@
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="16"/>
+      <c r="A46" s="21"/>
       <c r="B46" t="s">
         <v>6</v>
       </c>
@@ -2980,7 +5384,7 @@
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="16"/>
+      <c r="A47" s="21"/>
       <c r="B47" t="s">
         <v>7</v>
       </c>
@@ -3034,7 +5438,7 @@
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
+      <c r="A48" s="21"/>
       <c r="B48" t="s">
         <v>7</v>
       </c>
@@ -3088,7 +5492,7 @@
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
+      <c r="A49" s="21"/>
       <c r="B49" t="s">
         <v>8</v>
       </c>
@@ -3142,7 +5546,7 @@
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="16"/>
+      <c r="A50" s="21"/>
       <c r="B50" t="s">
         <v>8</v>
       </c>
@@ -3196,7 +5600,7 @@
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
+      <c r="A51" s="21"/>
       <c r="B51" t="s">
         <v>9</v>
       </c>
@@ -3250,7 +5654,7 @@
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="16"/>
+      <c r="A52" s="21"/>
       <c r="B52" t="s">
         <v>9</v>
       </c>
@@ -3304,7 +5708,7 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="16"/>
+      <c r="A53" s="21"/>
       <c r="B53" t="s">
         <v>10</v>
       </c>
@@ -3358,7 +5762,7 @@
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="16"/>
+      <c r="A54" s="21"/>
       <c r="B54" t="s">
         <v>10</v>
       </c>
@@ -3413,6 +5817,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="N29:R29"/>
+    <mergeCell ref="A43:A54"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="I43:M43"/>
+    <mergeCell ref="N43:R43"/>
+    <mergeCell ref="A29:A40"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="I29:M29"/>
     <mergeCell ref="A1:A12"/>
     <mergeCell ref="N1:R1"/>
     <mergeCell ref="A15:A26"/>
@@ -3425,31 +5841,19 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="I1:M1"/>
-    <mergeCell ref="N29:R29"/>
-    <mergeCell ref="A43:A54"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="I43:M43"/>
-    <mergeCell ref="N43:R43"/>
-    <mergeCell ref="A29:A40"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="I29:M29"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A15" r:id="rId1"/>
-    <hyperlink ref="A29" r:id="rId2"/>
-    <hyperlink ref="A43" r:id="rId3"/>
+    <hyperlink ref="A15" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="A29" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="A43" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -3466,86 +5870,86 @@
     <col min="16" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="21"/>
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -3595,8 +5999,8 @@
         <v>0.36299292452830101</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="21"/>
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -3645,9 +6049,13 @@
       <c r="Q4" s="7">
         <v>0.23597764235967</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
+      <c r="W4" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" s="27"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="21"/>
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -3696,9 +6104,24 @@
       <c r="Q5" s="7">
         <v>0.24283048484848499</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="V5" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="W5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="X5" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="21"/>
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -3747,9 +6170,24 @@
       <c r="Q6" s="7">
         <v>0.243209452736318</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+      <c r="V6" t="s">
+        <v>6</v>
+      </c>
+      <c r="W6" s="7">
+        <v>0.59070933545747795</v>
+      </c>
+      <c r="X6" s="7">
+        <v>0.61368135517871603</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>0.38527400641204301</v>
+      </c>
+      <c r="Z6" s="14">
+        <v>0.38527400641204301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="21"/>
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -3798,87 +6236,151 @@
       <c r="Q7" s="7">
         <v>0.16797006911217499</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="V7" t="s">
+        <v>7</v>
+      </c>
+      <c r="W7" s="7">
+        <v>0.41923681344692598</v>
+      </c>
+      <c r="X7" s="7">
+        <v>0.44614609614102302</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>0.50305442500813802</v>
+      </c>
+      <c r="Z7" s="14">
+        <v>0.50295389144647495</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V8" t="s">
+        <v>8</v>
+      </c>
+      <c r="W8" s="7">
+        <v>0.397331927022603</v>
+      </c>
+      <c r="X8" s="7">
+        <v>0.42534738888306001</v>
+      </c>
+      <c r="Y8" s="14">
+        <v>0.48339878915141998</v>
+      </c>
+      <c r="Z8" s="14">
+        <v>0.48337464720790402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V9" t="s">
+        <v>9</v>
+      </c>
+      <c r="W9" s="7">
+        <v>0.42135339471191002</v>
+      </c>
+      <c r="X9" s="7">
+        <v>0.44836102296365599</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>0.47542251987224898</v>
+      </c>
+      <c r="Z9" s="14">
+        <v>0.47541460287138898</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="15" t="s">
+      <c r="C10" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="V10" t="s">
+        <v>10</v>
+      </c>
+      <c r="W10" s="7">
+        <v>0.25917847212414402</v>
+      </c>
+      <c r="X10" s="7">
+        <v>0.28640208375623799</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>0.42632310636204301</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>0.42625040488487198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="G11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="K11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="L11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="P11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="Q11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
       <c r="B12" t="s">
         <v>6</v>
       </c>
@@ -3928,8 +6430,8 @@
         <v>0.28811886792452701</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -3979,8 +6481,8 @@
         <v>0.17542674108970599</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -4030,8 +6532,8 @@
         <v>0.18695200000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
       <c r="B15" t="s">
         <v>9</v>
       </c>
@@ -4080,9 +6582,21 @@
       <c r="Q15" s="7">
         <v>0.17891927860696499</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
+      <c r="W15" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z15" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
       <c r="B16" t="s">
         <v>10</v>
       </c>
@@ -4131,87 +6645,151 @@
       <c r="Q16" s="7">
         <v>0.13850308346624099</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="W16" t="s">
+        <v>6</v>
+      </c>
+      <c r="X16" s="7">
+        <v>0.519502733480118</v>
+      </c>
+      <c r="Y16" s="14">
+        <v>0.385488264884293</v>
+      </c>
+      <c r="Z16" s="8">
+        <v>0.38503348238878199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="W17" t="s">
+        <v>7</v>
+      </c>
+      <c r="X17" s="7">
+        <v>0.38496465732607199</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>0.50638092228877496</v>
+      </c>
+      <c r="Z17" s="8">
+        <v>0.61973888754940198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="W18" t="s">
+        <v>8</v>
+      </c>
+      <c r="X18" s="7">
+        <v>0.36254670075916001</v>
+      </c>
+      <c r="Y18" s="14">
+        <v>0.48804357159362599</v>
+      </c>
+      <c r="Z18" s="8">
+        <v>0.60433751348826104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="W19" t="s">
+        <v>9</v>
+      </c>
+      <c r="X19" s="7">
+        <v>0.389080504930851</v>
+      </c>
+      <c r="Y19" s="14">
+        <v>0.47818063909208902</v>
+      </c>
+      <c r="Z19" s="8">
+        <v>0.60418008525687406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
       <c r="C20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="G20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H20" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="K20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="L20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="P20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="6" t="s">
+      <c r="Q20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
+      <c r="W20" t="s">
+        <v>10</v>
+      </c>
+      <c r="X20" s="7">
+        <v>0.23199580861774199</v>
+      </c>
+      <c r="Y20" s="14">
+        <v>0.43327115108686198</v>
+      </c>
+      <c r="Z20" s="8">
+        <v>0.53310659993139498</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
       <c r="B21" t="s">
         <v>6</v>
       </c>
@@ -4261,8 +6839,8 @@
         <v>0.21757075471698101</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
       <c r="B22" t="s">
         <v>7</v>
       </c>
@@ -4311,9 +6889,12 @@
       <c r="Q22" s="7">
         <v>0.13980468557968301</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
+      <c r="X22" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
       <c r="B23" t="s">
         <v>8</v>
       </c>
@@ -4363,8 +6944,8 @@
         <v>0.15118109090908999</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A24" s="21"/>
       <c r="B24" t="s">
         <v>9</v>
       </c>
@@ -4414,8 +6995,8 @@
         <v>0.14317139303482601</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
       <c r="B25" t="s">
         <v>10</v>
       </c>
@@ -4465,86 +7046,86 @@
         <v>0.117611137692717</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
       <c r="C29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="G29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H29" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="K29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="L29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M29" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O29" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N29" s="6" t="s">
+      <c r="P29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O29" s="6" t="s">
+      <c r="Q29" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
       <c r="B30" t="s">
         <v>6</v>
       </c>
@@ -4594,8 +7175,8 @@
         <v>0.17758018867924599</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A31" s="21"/>
       <c r="B31" t="s">
         <v>7</v>
       </c>
@@ -4645,8 +7226,8 @@
         <v>0.116839758295779</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
       <c r="B32" t="s">
         <v>8</v>
       </c>
@@ -4697,7 +7278,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
+      <c r="A33" s="21"/>
       <c r="B33" t="s">
         <v>9</v>
       </c>
@@ -4748,7 +7329,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
+      <c r="A34" s="21"/>
       <c r="B34" t="s">
         <v>10</v>
       </c>
@@ -4799,7 +7380,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="A28:A34"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:L28"/>
+    <mergeCell ref="M28:Q28"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:L19"/>
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="A10:A16"/>
     <mergeCell ref="B10:B11"/>
@@ -4810,29 +7402,26 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="H1:L1"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="A28:A34"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:L28"/>
-    <mergeCell ref="M28:Q28"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:L19"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A10" r:id="rId1"/>
-    <hyperlink ref="A19" r:id="rId2"/>
-    <hyperlink ref="A28" r:id="rId3"/>
+    <hyperlink ref="A10" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="A19" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="A28" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="X5" r:id="rId4" xr:uid="{D3217428-9DCB-45F8-8B4A-268A89AD2A57}"/>
+    <hyperlink ref="W5" r:id="rId5" xr:uid="{1137AACE-438D-4F6A-86B8-D62B674792D0}"/>
+    <hyperlink ref="Y5" r:id="rId6" xr:uid="{DAC79226-7194-474E-BBE5-1377EBE2F639}"/>
+    <hyperlink ref="Z5" r:id="rId7" xr:uid="{0E48204D-24E9-45BF-966E-85F7A14BC465}"/>
+    <hyperlink ref="X22" r:id="rId8" xr:uid="{61F9CD0F-423E-45D2-8339-EE47CE1C281F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId9"/>
+  <drawing r:id="rId10"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:X22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -4849,86 +7438,86 @@
     <col min="16" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="21"/>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
@@ -4978,8 +7567,8 @@
         <v>0.219520161144828</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="21"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -5029,86 +7618,121 @@
         <v>0.24529251336897601</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="17" t="s">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="V6" t="s">
+        <v>42</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="15" t="s">
+      <c r="C7" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="U7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="V7" s="7">
+        <v>0.35580137223333003</v>
+      </c>
+      <c r="W7" s="14">
+        <v>0.521014872790316</v>
+      </c>
+      <c r="X7" s="8">
+        <v>0.62367526026213604</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="G8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="L8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="Q8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
+      <c r="U8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" s="7">
+        <v>0.37792989198736099</v>
+      </c>
+      <c r="W8" s="14">
+        <v>0.44109788431775299</v>
+      </c>
+      <c r="X8" s="8">
+        <v>0.56429030658716905</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -5158,8 +7782,8 @@
         <v>0.163598833503696</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
@@ -5209,86 +7833,86 @@
         <v>0.188786211596943</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="G14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="K14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="L14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="P14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O14" s="6" t="s">
+      <c r="Q14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P14" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
@@ -5338,8 +7962,8 @@
         <v>0.130992784558953</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
@@ -5390,85 +8014,85 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="G20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H20" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="K20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="L20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="P20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="6" t="s">
+      <c r="Q20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
@@ -5519,7 +8143,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
@@ -5571,6 +8195,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:L13"/>
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="B7:B8"/>
@@ -5581,22 +8215,13 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="H1:L1"/>
-    <mergeCell ref="M13:Q13"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:L13"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1"/>
-    <hyperlink ref="A13" r:id="rId2"/>
-    <hyperlink ref="A19" r:id="rId3"/>
+    <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="A13" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="A19" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>